--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104656_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104656_W22.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4731</v>
+        <v>4.542</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0144</v>
+        <v>1.45</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4587</v>
+        <v>3.0921</v>
       </c>
       <c r="G2" t="n">
-        <v>3.63</v>
+        <v>2.9093</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0493</v>
+        <v>2.2403</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5807</v>
+        <v>0.669</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4503</v>
+        <v>2.4191</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8533</v>
+        <v>2.8441</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5971</v>
+        <v>-0.4249</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1797</v>
+        <v>0.4901</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.6037</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9837</v>
+        <v>1.0939</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>3.482</v>
+        <v>1.475</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3107</v>
+        <v>0.2388</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1713</v>
+        <v>1.2361</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.639</v>
+        <v>0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.116</v>
+        <v>3.7958</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0536</v>
+        <v>2.396</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0624</v>
+        <v>1.3998</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9088</v>
+        <v>3.6171</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2424</v>
+        <v>2.0288</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6664</v>
+        <v>1.5883</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4414</v>
+        <v>3.4152</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8573</v>
+        <v>2.8194</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4159</v>
+        <v>0.5958</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4674</v>
+        <v>0.2019</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6149</v>
+        <v>-0.7906</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0823</v>
+        <v>0.9925</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0465</v>
+        <v>1.8129</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1875</v>
+        <v>0.7336</v>
       </c>
       <c r="U3" t="n">
-        <v>1.234</v>
+        <v>1.0793</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>-1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1231</v>
+        <v>3.6907</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1249</v>
+        <v>2.8401</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0018</v>
+        <v>0.8506</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4567</v>
+        <v>4.2388</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8169999999999999</v>
+        <v>2.2576</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2737</v>
+        <v>1.9812</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0376</v>
+        <v>4.3804</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7623</v>
+        <v>2.8613</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.7247</v>
+        <v>1.519</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4944</v>
+        <v>-0.1416</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9453</v>
+        <v>-0.6037</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.549</v>
+        <v>0.4622</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.3624</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6956</v>
+        <v>-0.1745</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2243</v>
+        <v>0.5369</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8243</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>4.917</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8471</v>
+        <v>3.4334</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2061</v>
+        <v>3.6572</v>
       </c>
       <c r="F5" t="n">
-        <v>0.641</v>
+        <v>-0.2238</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2402</v>
+        <v>-1.4784</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2597</v>
+        <v>0.7994</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9805</v>
+        <v>-2.2778</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4019</v>
+        <v>-0.0025</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8746</v>
+        <v>1.7334</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5273</v>
+        <v>-1.7359</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1617</v>
+        <v>-1.4759</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6149</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4532</v>
+        <v>-0.5419</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4857</v>
+        <v>0.871</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8347</v>
+        <v>-0.1048</v>
       </c>
       <c r="U5" t="n">
-        <v>0.349</v>
+        <v>0.9758</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3.8132</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>4.9026</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3556</v>
+        <v>2.071</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2522</v>
+        <v>1.6828</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1034</v>
+        <v>0.3882</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0412</v>
+        <v>-2.0568</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.5134</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5407</v>
+        <v>-1.5434</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2356</v>
+        <v>-0.2797</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8547</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.0903</v>
+        <v>-1.1029</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8056</v>
+        <v>-1.777</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3552</v>
+        <v>-1.3365</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0773</v>
+        <v>0.8106</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5293</v>
+        <v>0.0112</v>
       </c>
       <c r="U6" t="n">
-        <v>0.548</v>
+        <v>0.7994</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4572</v>
+        <v>0.6479</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8583</v>
+        <v>0.7389</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4012</v>
+        <v>-0.091</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.494</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.511</v>
+        <v>-0.5003</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0026</v>
+        <v>0.0064</v>
       </c>
       <c r="J7" t="n">
-        <v>0.698</v>
+        <v>0.695</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2116</v>
+        <v>-1.189</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2241</v>
+        <v>0.3891</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1603</v>
+        <v>0.0439</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0638</v>
+        <v>0.3452</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1792</v>
+        <v>0.1215</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0287</v>
+        <v>0.2564</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2079</v>
+        <v>-0.1348</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0602</v>
+        <v>-0.0621</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5888</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6504</v>
+        <v>-0.651</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3765</v>
+        <v>0.368</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1256</v>
+        <v>1.1204</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4368</v>
+        <v>-0.4301</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,22 +1078,22 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0417</v>
+        <v>0.3414</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3478</v>
+        <v>-0.1116</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3895</v>
+        <v>0.4531</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4237</v>
+        <v>-2.3696</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7776</v>
+        <v>-0.5612</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6462</v>
+        <v>-1.8084</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5105</v>
+        <v>-1.5152</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9161</v>
+        <v>-0.9271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5944</v>
+        <v>-0.5881</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2211</v>
+        <v>-0.2405</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.333</v>
+        <v>-0.3522</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2894</v>
+        <v>-1.2747</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0472</v>
+        <v>0.0953</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6037</v>
+        <v>0.416</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="10">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5638</v>
+        <v>-2.4916</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0152</v>
+        <v>-0.016</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5486</v>
+        <v>-2.4756</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0335</v>
+        <v>0.038</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2121</v>
+        <v>0.2152</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1786</v>
+        <v>-0.1772</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1239</v>
+        <v>0.1234</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0854</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,22 +1234,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4119</v>
+        <v>-0.3507</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8215</v>
+        <v>-3.7204</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6248</v>
+        <v>-6.25</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8032</v>
+        <v>2.5296</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4491</v>
+        <v>-3.4605</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3029</v>
+        <v>-2.3088</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1462</v>
+        <v>-1.1517</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.8775</v>
+        <v>-2.9165</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9635</v>
+        <v>-0.9867</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.914</v>
+        <v>-1.9298</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5716</v>
+        <v>-0.5441</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6029</v>
+        <v>1.7189</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1179</v>
+        <v>0.3085</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7209</v>
+        <v>1.4104</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.383899999999997</v>
+        <v>9.720700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>6.1206</v>
+        <v>6.194199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.262999999999999</v>
+        <v>3.5267</v>
       </c>
       <c r="G12" t="n">
-        <v>1.781200000000001</v>
+        <v>1.736200000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>3.940200000000001</v>
+        <v>3.8805</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.159</v>
+        <v>-2.1443</v>
       </c>
       <c r="J12" t="n">
-        <v>8.195400000000003</v>
+        <v>7.961899999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>11.7413</v>
+        <v>11.5695</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.545599999999999</v>
+        <v>-3.6077</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.4144</v>
+        <v>-6.2258</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.8009</v>
+        <v>-7.688899999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3868</v>
+        <v>1.463300000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.0733</v>
+        <v>-9.1053</v>
       </c>
       <c r="R12" t="n">
-        <v>9.073399999999999</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>7.1528</v>
+        <v>7.5259</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1212000000000002</v>
+        <v>0.485</v>
       </c>
       <c r="U12" t="n">
-        <v>7.031700000000001</v>
+        <v>7.040900000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4498</v>
+        <v>0.4584000000000005</v>
       </c>
       <c r="W12" t="n">
-        <v>6.8774</v>
+        <v>6.8523</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.4276</v>
+        <v>-6.394</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1975</v>
+        <v>3.1757</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6917</v>
+        <v>1.7599</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5058</v>
+        <v>1.4158</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6068</v>
+        <v>1.6011</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2496</v>
+        <v>1.2466</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3572</v>
+        <v>0.3544</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7384</v>
+        <v>1.7002</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3062</v>
+        <v>2.2818</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1316</v>
+        <v>-0.0992</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0566</v>
+        <v>-1.0351</v>
       </c>
       <c r="O13" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1844</v>
+        <v>-1.1962</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4608</v>
+        <v>-1.3453</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2764</v>
+        <v>0.1492</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1237</v>
+        <v>2.3136</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2226</v>
+        <v>1.4432</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9011</v>
+        <v>0.8704</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5213</v>
+        <v>1.5354</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1138</v>
+        <v>0.123</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4074</v>
+        <v>1.4124</v>
       </c>
       <c r="J14" t="n">
-        <v>2.266</v>
+        <v>2.2518</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9973</v>
+        <v>0.9858</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7447</v>
+        <v>-0.7164</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8834</v>
+        <v>-0.8628</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7585</v>
+        <v>-0.5876</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0434</v>
+        <v>-0.8087</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2849</v>
+        <v>0.2211</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4779</v>
+        <v>1.5272</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2095</v>
+        <v>1.2988</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2684</v>
+        <v>0.2285</v>
       </c>
       <c r="G15" t="n">
-        <v>3.056</v>
+        <v>3.0556</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2062</v>
+        <v>1.2117</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8498</v>
+        <v>1.8439</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0177</v>
+        <v>2.9972</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6797</v>
+        <v>1.672</v>
       </c>
       <c r="L15" t="n">
-        <v>1.338</v>
+        <v>1.3252</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0383</v>
+        <v>0.0584</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.8455</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8347</v>
+        <v>-0.718</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0629</v>
+        <v>-0.1275</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3004</v>
+        <v>1.1414</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9557</v>
+        <v>1.0594</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3446</v>
+        <v>0.082</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5036</v>
+        <v>-1.4905</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9914</v>
+        <v>-1.9822</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4878</v>
+        <v>0.4917</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6251</v>
+        <v>-0.629</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8784999999999999</v>
+        <v>-0.8615</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3814</v>
+        <v>-0.547</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7652</v>
+        <v>-0.6483</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3838</v>
+        <v>0.1013</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1217</v>
+        <v>-1.3143</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5973</v>
+        <v>-0.0525</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.719</v>
+        <v>-1.2618</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4029</v>
+        <v>0.0028</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9076</v>
+        <v>-0.1551</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4954</v>
+        <v>0.1579</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5129</v>
+        <v>0.0172</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0625</v>
+        <v>0.0172</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.5754</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8901</v>
+        <v>-0.0144</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9701</v>
+        <v>-0.1724</v>
       </c>
       <c r="O17" t="n">
-        <v>0.08</v>
+        <v>0.1579</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6669</v>
+        <v>-0.2276</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8983</v>
+        <v>-0.0697</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2314</v>
+        <v>-0.1579</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3181</v>
+        <v>-2.0556</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0522</v>
+        <v>-2.2665</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2658</v>
+        <v>0.2109</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0014</v>
+        <v>-2.1705</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1559</v>
+        <v>-1.2243</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1573</v>
+        <v>-0.9463</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0173</v>
+        <v>-1.667</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>0.0689</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.7359</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0159</v>
+        <v>-0.5036</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1732</v>
+        <v>-1.2932</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1573</v>
+        <v>0.7896</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2268</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>-0.5995</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1573</v>
+        <v>0.0316</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3922</v>
+        <v>-2.388</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4902</v>
+        <v>0.1254</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0979</v>
+        <v>-2.5134</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1766</v>
+        <v>-2.4074</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2383</v>
+        <v>-0.9103</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9383</v>
+        <v>-1.4971</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6554</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0693</v>
+        <v>1.03</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.7247</v>
+        <v>-1.587</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5212</v>
+        <v>-1.8505</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3075</v>
+        <v>-1.9403</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7864</v>
+        <v>0.0898</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8961</v>
+        <v>-0.5936</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8347</v>
+        <v>-0.5162</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0614</v>
+        <v>-0.0774</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6904</v>
+        <v>-2.6237</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2882</v>
+        <v>-1.2928</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4022</v>
+        <v>-1.3309</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1801</v>
+        <v>0.1835</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1717</v>
+        <v>-0.1696</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3519</v>
+        <v>0.3531</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0546</v>
+        <v>0.0545</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3242</v>
+        <v>-0.2625</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4195</v>
+        <v>-3.0565</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6968</v>
+        <v>-2.4987</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7227</v>
+        <v>-0.5578</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3174</v>
+        <v>-2.3132</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.6047</v>
+        <v>-3.5909</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2874</v>
+        <v>1.2777</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1714</v>
+        <v>-0.2034</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3201</v>
+        <v>-1.3347</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1487</v>
+        <v>1.1313</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.146</v>
+        <v>-2.1098</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.2847</v>
+        <v>-2.2561</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5558</v>
+        <v>-1.1986</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3912</v>
+        <v>-1.1572</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1645</v>
+        <v>-0.0414</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.5415</v>
+        <v>-6.0918</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4126</v>
+        <v>-3.1028</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1289</v>
+        <v>-2.9891</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2536</v>
+        <v>0.2671</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5597</v>
+        <v>1.5704</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3061</v>
+        <v>-1.3033</v>
       </c>
       <c r="J22" t="n">
-        <v>2.285</v>
+        <v>2.2611</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6711</v>
+        <v>3.6542</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0314</v>
+        <v>-1.994</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.1115</v>
+        <v>-2.0838</v>
       </c>
       <c r="O22" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5948</v>
+        <v>-1.151</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3217</v>
+        <v>-0.969</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2731</v>
+        <v>-0.1819</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.383900000000001</v>
+        <v>-9.372</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.263200000000001</v>
+        <v>-3.5266</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.120799999999999</v>
+        <v>-5.845399999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.781299999999999</v>
+        <v>-1.7361</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.9403</v>
+        <v>-3.8807</v>
       </c>
       <c r="I23" t="n">
-        <v>2.159</v>
+        <v>2.1444</v>
       </c>
       <c r="J23" t="n">
-        <v>6.4142</v>
+        <v>6.2256</v>
       </c>
       <c r="K23" t="n">
-        <v>7.800800000000001</v>
+        <v>7.6889</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.386699999999999</v>
+        <v>-1.4633</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.195600000000001</v>
+        <v>-7.962</v>
       </c>
       <c r="N23" t="n">
-        <v>-11.7413</v>
+        <v>-11.5696</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5456</v>
+        <v>3.6076</v>
       </c>
       <c r="P23" t="n">
-        <v>0.000100000000000211</v>
+        <v>0.000199999999999978</v>
       </c>
       <c r="Q23" t="n">
-        <v>-9.073499999999999</v>
+        <v>-9.105399999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>9.0733</v>
+        <v>9.1053</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.1528</v>
+        <v>-7.177599999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-7.031699999999999</v>
+        <v>-7.040999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1210000000000001</v>
+        <v>-0.1363</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.4498000000000002</v>
+        <v>-0.4583999999999997</v>
       </c>
       <c r="W23" t="n">
-        <v>6.4277</v>
+        <v>6.394</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.8774</v>
+        <v>-6.852300000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104656_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104656_W22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-6.394</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104656_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-6.852300000000001</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
